--- a/outputs/estruturas-20261015/Estruturas_Helte_2026-10-15.xlsx
+++ b/outputs/estruturas-20261015/Estruturas_Helte_2026-10-15.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Telhado: placas arredondadas pra par, em blocos de 4 placas + no máximo 1 bloco de 2. Ex.: 13 placas → 14 → 3 blocos de 4 + 1 de 2. Solo: mesas inteiras.</t>
+          <t>O kit mantém o número exato de placas (13 placas = 13 módulos). Só a ESTRUTURA vem dimensionada como a Helte manda: em blocos de 4 + no máximo 1 de 2, contando a próxima quantidade par (13 placas → estrutura de 14 = 3 blocos de 4 + 1 de 2). Solo: mesas inteiras.</t>
         </is>
       </c>
     </row>
